--- a/calibration_plots/plot_data_wine_smpbart.xlsx
+++ b/calibration_plots/plot_data_wine_smpbart.xlsx
@@ -368,23 +368,23 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.7811111111111111</v>
+        <v>0.8085</v>
       </c>
       <c r="B2">
-        <v>0.8</v>
+        <v>0.8055555555555556</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.9683333333333334</v>
+        <v>0.9795555555555555</v>
       </c>
       <c r="B3">
-        <v>0.9666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.9939607843137255</v>
+        <v>0.9967407407407407</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -392,7 +392,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.9996587301587302</v>
+        <v>0.9999523809523809</v>
       </c>
       <c r="B5">
         <v>1</v>
